--- a/consent_forms/036_emergency_contact_authorization_form--consent_forms.xlsx
+++ b/consent_forms/036_emergency_contact_authorization_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'5.1.1',_'name':_'stepparent',_'label':_'stepparent'}</t>
+          <t>stepparent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '5.1.1', 'name': 'stepparent', 'label': 'Stepparent'}</t>
+          <t>Stepparent</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'5.1.2',_'name':_'guardian',_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '5.1.2', 'name': 'guardian', 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'sibling',_'label':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'sibling', 'label': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'5.2.1',_'name':_'half_sibiling',_'label':_'half_sibling'}</t>
+          <t>half_sibling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '5.2.1', 'name': 'half_sibiling', 'label': 'Half Sibling'}</t>
+          <t>Half Sibling</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'5.2.2',_'name':_'other_sibling',_'label':_'other_sibling'}</t>
+          <t>other_sibling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '5.2.2', 'name': 'other_sibling', 'label': 'Other Sibling'}</t>
+          <t>Other Sibling</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'name':_'mother',_'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'name': 'mother', 'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'6.1.1',_'name':_'stepmother',_'label':_'stepmother'}</t>
+          <t>stepmother</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '6.1.1', 'name': 'stepmother', 'label': 'Stepmother'}</t>
+          <t>Stepmother</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'name':_'father',_'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'name': 'father', 'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'6.2.1',_'name':_'stepfather',_'label':_'stepfather'}</t>
+          <t>stepfather</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '6.2.1', 'name': 'stepfather', 'label': 'Stepfather'}</t>
+          <t>Stepfather</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'name':_'sister',_'label':_'sister'}</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'name': 'sister', 'label': 'Sister'}</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'6.3.1',_'name':_'half_sister',_'label':_'half_sister'}</t>
+          <t>half_sister</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '6.3.1', 'name': 'half_sister', 'label': 'Half Sister'}</t>
+          <t>Half Sister</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6.4,_'name':_'brother',_'label':_'brother'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6.4, 'name': 'brother', 'label': 'Brother'}</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'6.4.1',_'name':_'half_brother',_'label':_'half_brother'}</t>
+          <t>half_brother</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '6.4.1', 'name': 'half_brother', 'label': 'Half Brother'}</t>
+          <t>Half Brother</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'6.4.2',_'name':_'other_brother',_'label':_'other_brother'}</t>
+          <t>other_brother</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '6.4.2', 'name': 'other_brother', 'label': 'Other Brother'}</t>
+          <t>Other Brother</t>
         </is>
       </c>
     </row>
